--- a/doc/RiskMatrix.xlsx
+++ b/doc/RiskMatrix.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1"/>
+    <workbookView windowWidth="25620" windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="Matrix" sheetId="1" r:id="rId1"/>
     <sheet name="Risk" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -21,6 +29,18 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>NO.</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description of Risk</t>
+  </si>
+  <si>
+    <t>LIKELIHOOD</t>
+  </si>
   <si>
     <t>IMPACT</t>
   </si>
@@ -46,39 +66,22 @@
   <si>
     <t>Notes</t>
   </si>
-  <si>
-    <t>NO.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description of Risk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIKELIHOOD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -87,7 +90,172 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -95,24 +263,10 @@
       <sz val="14"/>
       <color rgb="FF76CED9"/>
       <name val="Arial Black"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,48 +281,234 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D8B6D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3D8B6D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -207,13 +547,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="dotted">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="dotted">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="dotted">
         <color auto="1"/>
       </top>
       <bottom style="dotted">
@@ -231,7 +586,7 @@
       <top style="dotted">
         <color auto="1"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -246,7 +601,7 @@
       <top style="dotted">
         <color auto="1"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -258,56 +613,139 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="dotted">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="dotted">
-        <color auto="1"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="dotted">
-        <color auto="1"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="dotted">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="dotted">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="dotted">
-        <color auto="1"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="dotted">
-        <color auto="1"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -321,319 +759,260 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="MAIN TITLE" xfId="1"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="MAIN TITLE" xfId="49"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="4">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -643,15 +1022,12 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -665,15 +1041,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="文本框 2"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6604000" y="508000"/>
-          <a:ext cx="2120900" cy="476250"/>
+          <a:off x="1280160" y="579120"/>
+          <a:ext cx="1998980" cy="582930"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -731,15 +1107,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="文本框 3"/>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="5480050" y="1708150"/>
-          <a:ext cx="1454150" cy="476250"/>
+          <a:off x="65405" y="2032635"/>
+          <a:ext cx="1676400" cy="476250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -844,7 +1220,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -879,7 +1255,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1053,29 +1429,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C7:H12"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="4.75" customWidth="1"/>
-    <col min="4" max="4" width="5.08203125" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" customWidth="1"/>
-    <col min="7" max="7" width="4.9140625" customWidth="1"/>
+    <col min="4" max="4" width="5.08035714285714" customWidth="1"/>
+    <col min="5" max="5" width="4.33035714285714" customWidth="1"/>
+    <col min="6" max="6" width="4.66071428571429" customWidth="1"/>
+    <col min="7" max="7" width="4.91071428571429" customWidth="1"/>
     <col min="8" max="8" width="4.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
+    <row r="7" ht="26" spans="3:8">
       <c r="C7" s="4"/>
       <c r="D7" s="5">
         <v>1</v>
@@ -1089,104 +1460,104 @@
       <c r="G7" s="5">
         <v>4</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="C8" s="7">
+    <row r="8" ht="26" spans="3:8">
+      <c r="C8" s="6">
         <v>5</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>5</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>10</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="12">
         <v>15</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="13">
         <v>20</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="14">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="C9" s="7">
-        <v>4</v>
-      </c>
-      <c r="D9" s="12">
-        <v>4</v>
-      </c>
-      <c r="E9" s="8">
+    <row r="9" ht="26" spans="3:8">
+      <c r="C9" s="6">
+        <v>4</v>
+      </c>
+      <c r="D9" s="8">
+        <v>4</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="12">
         <v>12</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="12">
         <v>16</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="C10" s="7">
+    <row r="10" ht="26" spans="3:8">
+      <c r="C10" s="6">
         <v>3</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="8">
         <v>3</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>6</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>9</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="12">
         <v>12</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="15">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="12">
-        <v>2</v>
-      </c>
-      <c r="E11" s="12">
-        <v>4</v>
-      </c>
-      <c r="F11" s="8">
+    <row r="11" ht="26" spans="3:8">
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8">
+        <v>4</v>
+      </c>
+      <c r="F11" s="7">
         <v>6</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>8</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="16">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="22.5" x14ac:dyDescent="0.45">
-      <c r="C12" s="15">
+    <row r="12" ht="26" spans="3:8">
+      <c r="C12" s="9">
         <v>1</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="10">
         <v>1</v>
       </c>
-      <c r="E12" s="16">
-        <v>2</v>
-      </c>
-      <c r="F12" s="16">
+      <c r="E12" s="10">
+        <v>2</v>
+      </c>
+      <c r="F12" s="10">
         <v>3</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="10">
         <v>4</v>
       </c>
       <c r="H12" s="17">
@@ -1194,59 +1565,60 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:K29"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.3303571428571" customWidth="1"/>
+    <col min="4" max="4" width="10.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="11.6607142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="39" x14ac:dyDescent="0.3">
+    <row r="2" ht="46" spans="1:11">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="4:6">
       <c r="D3">
         <v>2</v>
       </c>
@@ -1258,7 +1630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:6">
       <c r="D4">
         <v>2</v>
       </c>
@@ -1270,7 +1642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:6">
       <c r="D5">
         <v>5</v>
       </c>
@@ -1282,7 +1654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:6">
       <c r="D6">
         <v>2</v>
       </c>
@@ -1294,7 +1666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:6">
       <c r="D7">
         <v>1</v>
       </c>
@@ -1306,7 +1678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="5:6">
       <c r="E8">
         <v>2</v>
       </c>
@@ -1315,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:6">
       <c r="D9">
         <v>2</v>
       </c>
@@ -1327,7 +1699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:6">
       <c r="D10">
         <v>2</v>
       </c>
@@ -1339,7 +1711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:6">
       <c r="D11">
         <v>2</v>
       </c>
@@ -1351,7 +1723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:6">
       <c r="D12">
         <v>2</v>
       </c>
@@ -1363,7 +1735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:6">
       <c r="D13">
         <v>2</v>
       </c>
@@ -1375,7 +1747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:6">
       <c r="D14">
         <v>2</v>
       </c>
@@ -1387,7 +1759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:6">
       <c r="D15">
         <v>3</v>
       </c>
@@ -1399,7 +1771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:6">
       <c r="D16">
         <v>2</v>
       </c>
@@ -1411,7 +1783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:6">
       <c r="D17">
         <v>2</v>
       </c>
@@ -1423,7 +1795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:6">
       <c r="D18">
         <v>2</v>
       </c>
@@ -1435,7 +1807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:6">
       <c r="D19">
         <v>5</v>
       </c>
@@ -1447,7 +1819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:6">
       <c r="D20">
         <v>2</v>
       </c>
@@ -1459,7 +1831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:6">
       <c r="D21">
         <v>2</v>
       </c>
@@ -1471,7 +1843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:6">
       <c r="D22">
         <v>2</v>
       </c>
@@ -1483,7 +1855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:6">
       <c r="D23">
         <v>2</v>
       </c>
@@ -1495,7 +1867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:6">
       <c r="D24">
         <v>2</v>
       </c>
@@ -1507,7 +1879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:6">
       <c r="D25">
         <v>2</v>
       </c>
@@ -1516,28 +1888,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:4">
       <c r="D29">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <dataConsolidate/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="between">
+  <conditionalFormatting sqref="F$1:F$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>5</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>1</formula>
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="between">
       <formula>20</formula>
       <formula>25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
       <formula>11</formula>
       <formula>19</formula>
     </cfRule>
@@ -1548,5 +1918,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>